--- a/Extractive-QA/extractions-from-paper/synthetic_procedures.xlsx
+++ b/Extractive-QA/extractions-from-paper/synthetic_procedures.xlsx
@@ -28,7 +28,7 @@
     <t>Medium</t>
   </si>
   <si>
-    <t>Catalist</t>
+    <t>Catalyst</t>
   </si>
   <si>
     <t>Polymer class</t>
